--- a/config/excel/CfgLevels.xlsx
+++ b/config/excel/CfgLevels.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLevels" sheetId="1" r:id="Rfd7df8fec6e8444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLevels" sheetId="1" r:id="R47d7694614c74313"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,6 +394,9 @@
       <x:c r="M1" s="9" t="str">
         <x:v>LootPoolID</x:v>
       </x:c>
+      <x:c r="N1" t="str">
+        <x:v>LootLevel</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="10" t="str">
@@ -434,6 +437,9 @@
       </x:c>
       <x:c r="M2" s="10" t="str">
         <x:v>string</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>int</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
@@ -476,6 +482,9 @@
       <x:c r="M3" s="12" t="str">
         <x:v>箱子和NPC掉落池身份</x:v>
       </x:c>
+      <x:c r="N3" t="str">
+        <x:v># 掉落物品等级</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="6" t="n">
@@ -517,6 +526,9 @@
       <x:c r="M4" s="13" t="str">
         <x:v>default</x:v>
       </x:c>
+      <x:c r="N4" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="6" t="n">
@@ -557,6 +569,9 @@
       </x:c>
       <x:c r="M5" s="13" t="str">
         <x:v>default</x:v>
+      </x:c>
+      <x:c r="N5" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -598,6 +613,9 @@
       </x:c>
       <x:c r="M6" s="13" t="str">
         <x:v>default</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgLevels.xlsx
+++ b/config/excel/CfgLevels.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLevels" sheetId="1" r:id="R47d7694614c74313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgLevels" sheetId="1" r:id="R9ec2644e14e54b27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +49,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -63,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -119,6 +134,21 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -339,284 +369,272 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="23.100000381469727" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="15" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="15" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="15" t="str">
         <x:v>Description</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="15" t="str">
         <x:v>RequiredLevel</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
-        <x:v>GridWidth</x:v>
-      </x:c>
-      <x:c r="F1" s="9" t="str">
-        <x:v>GridHeight</x:v>
-      </x:c>
-      <x:c r="G1" s="9" t="str">
-        <x:v>ExtraConnectionMin</x:v>
-      </x:c>
-      <x:c r="H1" s="9" t="str">
-        <x:v>ExtraConnectionMax</x:v>
-      </x:c>
-      <x:c r="I1" s="9" t="str">
-        <x:v>LootRoomCount</x:v>
-      </x:c>
-      <x:c r="J1" s="9" t="str">
-        <x:v>ExtraExtractionChance</x:v>
-      </x:c>
-      <x:c r="K1" s="9" t="str">
-        <x:v>LayoutID</x:v>
-      </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="E1" s="15" t="str">
         <x:v>IsDefault</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="F1" s="15" t="str">
         <x:v>LootPoolID</x:v>
       </x:c>
-      <x:c r="N1" t="str">
+      <x:c r="G1" s="15" t="str">
         <x:v>LootLevel</x:v>
       </x:c>
+      <x:c r="H1" s="15" t="str">
+        <x:v>RegionCount</x:v>
+      </x:c>
+      <x:c r="I1" s="15" t="str">
+        <x:v>BossPoolID</x:v>
+      </x:c>
+      <x:c r="J1" s="15" t="str">
+        <x:v>FinalBossPoolID</x:v>
+      </x:c>
+      <x:c r="K1" s="15" t="str">
+        <x:v>ContentID</x:v>
+      </x:c>
+      <x:c r="L1" s="15" t="str">
+        <x:v>SkillPoolID</x:v>
+      </x:c>
+      <x:c r="M1" s="15" t="str">
+        <x:v>ProgressRuleID</x:v>
+      </x:c>
+      <x:c r="N1"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="16" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="str">
+      <x:c r="C2" s="16" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="10" t="str">
+      <x:c r="D2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="10" t="str">
+      <x:c r="E2" s="16" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="F2" s="16" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="G2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str">
+      <x:c r="H2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="I2" s="16" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="J2" s="16" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="K2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="L2" s="16" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="M2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="J2" s="10" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="K2" s="10" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="L2" s="10" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="N2"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="18" t="str">
         <x:v># 关卡编号</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="18" t="str">
         <x:v>关卡名称</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="18" t="str">
         <x:v>关卡说明</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="18" t="str">
         <x:v>解锁角色等级</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
-        <x:v>地图网格列数</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="str">
-        <x:v>地图网格行数</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="str">
-        <x:v>额外连接最小数</x:v>
-      </x:c>
-      <x:c r="H3" s="12" t="str">
-        <x:v>额外连接最大数</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="str">
-        <x:v>战利品房数量</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="str">
-        <x:v>额外撤离候选概率</x:v>
-      </x:c>
-      <x:c r="K3" s="12" t="str">
-        <x:v>房间布局编号</x:v>
-      </x:c>
-      <x:c r="L3" s="12" t="str">
+      <x:c r="E3" s="18" t="str">
         <x:v>旧入口使用的默认关卡</x:v>
       </x:c>
-      <x:c r="M3" s="12" t="str">
+      <x:c r="F3" s="18" t="str">
         <x:v>箱子和NPC掉落池身份</x:v>
       </x:c>
-      <x:c r="N3" t="str">
+      <x:c r="G3" s="18" t="str">
         <x:v># 掉落物品等级</x:v>
       </x:c>
+      <x:c r="H3" s="18" t="str">
+        <x:v>探索区域数量，不含最终场地</x:v>
+      </x:c>
+      <x:c r="I3" s="18" t="str">
+        <x:v>区域尾王独立池</x:v>
+      </x:c>
+      <x:c r="J3" s="18" t="str">
+        <x:v>关卡最终Boss池</x:v>
+      </x:c>
+      <x:c r="K3" s="18" t="str">
+        <x:v>区域内容配置</x:v>
+      </x:c>
+      <x:c r="L3" s="18" t="str">
+        <x:v>本关独立技能池</x:v>
+      </x:c>
+      <x:c r="M3" s="18" t="str">
+        <x:v>刷怪进度规则</x:v>
+      </x:c>
+      <x:c r="N3"/>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="13" t="str">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="19" t="str">
         <x:v>荒野遗迹</x:v>
       </x:c>
-      <x:c r="C4" s="13" t="str">
-        <x:v>探索相连区域，寻找战利品与撤离点</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="n">
+      <x:c r="C4" s="19" t="str">
+        <x:v>探索连续区域，完成尾王奖励后带回结束或继续深入</x:v>
+      </x:c>
+      <x:c r="D4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="19" t="str">
+        <x:v>default</x:v>
+      </x:c>
+      <x:c r="G4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I4" s="19" t="str">
+        <x:v>region</x:v>
+      </x:c>
+      <x:c r="J4" s="19" t="str">
+        <x:v>final</x:v>
+      </x:c>
+      <x:c r="K4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L4" s="19" t="str">
+        <x:v>expedition</x:v>
+      </x:c>
+      <x:c r="M4" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N4"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="19" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I4" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J4" s="6" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="K4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L4" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M4" s="13" t="str">
+      <x:c r="B5" s="19" t="str">
+        <x:v>深层遗迹</x:v>
+      </x:c>
+      <x:c r="C5" s="19" t="str">
+        <x:v>探索连续区域，完成尾王奖励后带回结束或继续深入</x:v>
+      </x:c>
+      <x:c r="D5" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="19" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="N4" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G5" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I5" s="19" t="str">
+        <x:v>region</x:v>
+      </x:c>
+      <x:c r="J5" s="19" t="str">
+        <x:v>final</x:v>
+      </x:c>
+      <x:c r="K5" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" s="19" t="str">
+        <x:v>expedition</x:v>
+      </x:c>
+      <x:c r="M5" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N5"/>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="13" t="str">
-        <x:v>深层遗迹</x:v>
-      </x:c>
-      <x:c r="C5" s="13" t="str">
-        <x:v>更强的敌人与更高等级的装备</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="n">
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="19" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="6" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J5" s="6" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="K5" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L5" s="7" t="b">
+      <x:c r="B6" s="19" t="str">
+        <x:v>禁地</x:v>
+      </x:c>
+      <x:c r="C6" s="19" t="str">
+        <x:v>探索连续区域，完成尾王奖励后带回结束或继续深入</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M5" s="13" t="str">
+      <x:c r="F6" s="19" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="N5" t="n">
+      <x:c r="G6" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="19" t="n">
         <x:v>3</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="13" t="str">
-        <x:v>禁地</x:v>
-      </x:c>
-      <x:c r="C6" s="13" t="str">
-        <x:v>高风险区域</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J6" s="6" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="K6" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L6" s="7" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="13" t="str">
-        <x:v>default</x:v>
-      </x:c>
-      <x:c r="N6" t="n">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="I6" s="19" t="str">
+        <x:v>region</x:v>
+      </x:c>
+      <x:c r="J6" s="19" t="str">
+        <x:v>final</x:v>
+      </x:c>
+      <x:c r="K6" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L6" s="19" t="str">
+        <x:v>expedition</x:v>
+      </x:c>
+      <x:c r="M6" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
